--- a/ai_logs/AI_AuditLog_Van.xlsx
+++ b/ai_logs/AI_AuditLog_Van.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15820" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="15760" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,6 +188,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -572,21 +573,21 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" style="19" min="1" max="1"/>
-    <col width="40" customWidth="1" style="19" min="2" max="2"/>
-    <col width="15" customWidth="1" style="19" min="3" max="3"/>
-    <col width="30" customWidth="1" style="19" min="4" max="4"/>
-    <col width="20" customWidth="1" style="19" min="5" max="6"/>
+    <col width="25" customWidth="1" style="20" min="1" max="1"/>
+    <col width="40" customWidth="1" style="20" min="2" max="2"/>
+    <col width="15" customWidth="1" style="20" min="3" max="3"/>
+    <col width="30" customWidth="1" style="20" min="4" max="4"/>
+    <col width="20" customWidth="1" style="20" min="5" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="19" customHeight="1" s="19">
+    <row r="3" ht="19" customHeight="1" s="20">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>STUDENT INFORMATION</t>
@@ -641,7 +642,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1" s="19">
+    <row r="9" ht="19" customHeight="1" s="20">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>AI USAGE SUMMARY</t>
@@ -700,14 +701,14 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1" s="19">
+    <row r="15" ht="19" customHeight="1" s="20">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>AI TOOLS USED</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" s="19">
+    <row r="16" ht="16" customHeight="1" s="20">
       <c r="A16" s="6" t="inlineStr">
         <is>
           <t>AI Tool</t>
@@ -729,7 +730,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1" s="19">
+    <row r="17" ht="16" customHeight="1" s="20">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>ChatGPT</t>
@@ -751,7 +752,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" s="19">
+    <row r="18" ht="16" customHeight="1" s="20">
       <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Claude</t>
@@ -773,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1" s="19">
+    <row r="19" ht="16" customHeight="1" s="20">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>GitHub Copilot</t>
@@ -795,7 +796,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" s="19">
+    <row r="20" ht="16" customHeight="1" s="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>[Add more...]</t>
@@ -805,14 +806,14 @@
       <c r="C20" s="7" t="n"/>
       <c r="D20" s="7" t="n"/>
     </row>
-    <row r="22" ht="19" customHeight="1" s="19">
+    <row r="22" ht="19" customHeight="1" s="20">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>CORE PROMPTS DISTRIBUTION BY DTC COMPONENT</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1" s="19">
+    <row r="23" ht="16" customHeight="1" s="20">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>DTC Component</t>
@@ -829,7 +830,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" s="19">
+    <row r="24" ht="16" customHeight="1" s="20">
       <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Decomposition</t>
@@ -844,7 +845,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1" s="19">
+    <row r="25" ht="16" customHeight="1" s="20">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Pattern Recognition</t>
@@ -859,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1" s="19">
+    <row r="26" ht="16" customHeight="1" s="20">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Abstraction</t>
@@ -874,7 +875,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1" s="19">
+    <row r="27" ht="16" customHeight="1" s="20">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Algorithms</t>
@@ -906,30 +907,30 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="19" min="1" max="1"/>
-    <col width="18" customWidth="1" style="19" min="2" max="3"/>
-    <col width="25" customWidth="1" style="19" min="4" max="4"/>
-    <col width="30" customWidth="1" style="19" min="5" max="5"/>
-    <col width="35" customWidth="1" style="19" min="6" max="6"/>
-    <col width="50" customWidth="1" style="19" min="7" max="7"/>
-    <col width="20" customWidth="1" style="19" min="8" max="8"/>
+    <col width="8" customWidth="1" style="20" min="1" max="1"/>
+    <col width="18" customWidth="1" style="20" min="2" max="3"/>
+    <col width="25" customWidth="1" style="20" min="4" max="4"/>
+    <col width="30" customWidth="1" style="20" min="5" max="5"/>
+    <col width="35" customWidth="1" style="20" min="6" max="6"/>
+    <col width="50" customWidth="1" style="20" min="7" max="7"/>
+    <col width="20" customWidth="1" style="20" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>DETAILED AI AUDIT LOG</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" s="19">
-      <c r="A2" s="20" t="inlineStr">
+    <row r="2" ht="30" customHeight="1" s="20">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>INSTRUCTIONS: Chỉ ghi CORE PROMPTS (Decision/Problem-Solving/Verification). Mỗi entry phải trả lời đầy đủ 4 câu hỏi trong Human Delta.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1" s="19">
+    <row r="3" ht="40" customHeight="1" s="20">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -971,7 +972,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="100" customHeight="1" s="19">
+    <row r="4" ht="100" customHeight="1" s="20">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>001</t>
@@ -979,164 +980,269 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>File I/O – CSV ID Format</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Cần xác định format ID chuẩn cho từng entity trong file CSV để đảm bảo nhất quán giữa seats.csv, tickets.csv và transactions.csv.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Hãy đề xuất format ID chuẩn cho các entity Seat, Ticket và BookingTransaction trong hệ thống đặt vé sân vận động lưu trữ bằng CSV. ID cần có tính đọc được, dễ sort và không trùng lặp.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>AI đề xuất dùng prefix kết hợp số thứ tự 0-padded: SEAT000001, TKT00000001, TXN00000001. Mỗi prefix phân biệt rõ loại entity, số thứ tự 6–8 chữ số giúp sort đúng thứ tự tự nhiên.</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Critical Thinking: Format này tuy dễ đọc nhưng nếu dùng số thứ tự tăng dần thì khi nhiều thread đặt vé đồng thời sẽ xảy ra race condition khi tạo ID.
+Contextualization: Hệ thống của nhóm hiện dùng DataGenerator sinh sẵn dữ liệu, không tạo ID tại runtime theo sequence mà dùng UUID substring để đảm bảo uniqueness.
+Creative Synthesis: Em kết hợp gợi ý của AI (prefix rõ ràng) với UUID: ví dụ TKT + 8 ký tự đầu UUID uppercase → TKT1A2B3C4D. Vừa unique, vừa readable.
+Decision: Áp dụng format TKT + UUID.substring(0,8).toUpperCase() trong BookingController.createTicket().</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Đoạn code createTicket() trong BookingController.java dòng ticketId generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="100" customHeight="1" s="20">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
           <t>PROBLEM-SOLVING</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Exception Handling</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Quản lý lỗi khi đọc dữ liệu không hợp lệ từ file CSV.</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Làm thế nào để xử lý các ngoại lệ khi đọc file CSV nếu định dạng dữ liệu ngày tháng không hợp lệ ở trường ngày diễn ra trận đấu mà không làm crash chương trình?</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>AI gợi ý dùng khối try-catch để bắt DateTimeParseException và in ra log, sau đó tiếp tục đọc dòng tiếp theo.</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Critical Thinking: AI chỉ in ra log thì admin sẽ không biết dòng nào bị lỗi.
-Contextualization: Cần báo lỗi cụ thể để kiểm tra lại file.
-Creative Synthesis: Em thiết kế một danh sách errorList lưu lại các dòng lỗi và hiển thị tổng hợp sau khi đọc xong.
-Decision: Áp dụng bắt lỗi và lưu vào list thay vì chỉ in ra console.</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Đoạn code try-catch trong CsvFileService và ảnh chụp màn hình cảnh báo lỗi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="100" customHeight="1" s="19">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>002</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>File I/O – Tránh Duplicate Entry CSV</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Khi đặt vé, nếu cùng một ghế trong cùng một trận đấu bị ghi hai lần vào tickets.csv sẽ gây ra Double Booking. Cần cơ chế kiểm tra trước khi ghi.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Làm thế nào để kiểm tra xem một cặp (seatId, matchId) đã tồn tại trong file tickets.csv hay chưa trước khi cho phép tạo vé mới? Hệ thống dùng Java đọc/ghi CSV thuần, không dùng Database.</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>AI gợi ý đọc toàn bộ file tickets.csv vào List, dùng Stream filter để kiểm tra: tickets.stream().anyMatch(t -&gt; t.getSeatId().equals(seatId) &amp;&amp; t.getMatchId().equals(matchId)).</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Critical Thinking: Cách này đúng về logic nhưng mỗi lần đặt vé phải đọc lại toàn bộ file CSV, nếu có 100,000 vé thì rất chậm.
+Contextualization: TicketRepository đã có sẵn phương thức existsBySeatAndMatch() được implement bằng findByCondition(Predicate&lt;T&gt;) — đây chính xác là cơ chế AI gợi ý nhưng đã được tối ưu sẵn trong codebase.
+Creative Synthesis: Em nhận ra không cần viết thêm logic mới, chỉ cần gọi ticketRepository.existsBySeatAndMatch(seatId, matchId) trong BookingController.bookSeat() là đủ và an toàn.
+Decision: Tích hợp existsBySeatAndMatch() làm double-check layer thứ hai sau khi kiểm tra SeatStatus.BOOKED, tạo 2 lớp bảo vệ chống Double Booking.</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>BookingController.java phần kiểm tra điều kiện trong bookSeat(): seat.getStatus() == SeatStatus.BOOKED || ticketRepository.existsBySeatAndMatch(seatId, matchId).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="100" customHeight="1" s="20">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Data Structure</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Lưu trữ danh sách vé đã bán để kiểm tra vé trống nhanh chóng.</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Cấu trúc dữ liệu nào tốt nhất để lưu trữ và tra cứu nhanh vé đã đặt trong ứng dụng Java?</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>AI gợi ý sử dụng ArrayList kết hợp với vòng lặp tìm kiếm tuyến tính (Linear Search).</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Critical Thinking: ArrayList tìm kiếm mất O(N), nếu vé lớn sẽ chậm.
-Contextualization: Ứng dụng booking thường xuyên check trạng thái vé.
-Creative Synthesis: Sử dụng HashSet lưu ID các vé đã bán, giảm thời gian tìm kiếm xuống O(1).
-Decision: Dùng HashSet chứa TicketID để tra cứu trạng thái vé.</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Code sử dụng HashSet trong TicketManager.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="100" customHeight="1" s="19">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>003</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Controller – Xử lý Exception trong bookSeat()</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Khi đặt vé thất bại do lỗi hệ thống (IOException, NullPointerException...), cần quyết định Transaction có nên được tạo ra hay không và với trạng thái gì.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Trong phương thức bookSeat(), nếu xảy ra Exception trong quá trình ghi file CSV, hệ thống có nên vẫn tạo BookingTransaction với status FAILED không? Hay bỏ qua và chỉ log lỗi?</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>AI khuyến nghị luôn tạo Transaction dù thành công hay thất bại, vì Transaction là audit trail quan trọng để theo dõi mọi attempt. Status FAILED ghi nhận attempt thất bại để phân tích sau.</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Critical Thinking: AI nói đúng về vai trò audit trail, nhưng nếu Exception xảy ra ngay trong lúc đang ghi Transaction thì sẽ tạo ra vòng lặp lỗi.
+Contextualization: Trong project LAB211, TransactionRepository dùng append() (ghi thêm vào cuối file) là operation nhẹ nhất, khả năng thất bại rất thấp so với save() (đọc-ghi toàn bộ file).
+Creative Synthesis: Em thiết kế try-catch bao quanh toàn bộ logic đặt vé, khối catch gọi createTransaction() với status FAILED. createTransaction() dùng append() nên tách biệt và ít rủi ro hơn.
+Decision: Áp dụng pattern try-catch-finally: luôn gọi createTransaction() ở cuối dù kết quả thế nào, dùng biến startTime đo durationMs.</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Cấu trúc try-catch trong BookingController.bookSeat() và hàm createTransaction() với TransactionStatus.FAILED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1" s="20">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>PROBLEM-SOLVING</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Controller – Khôi phục Seat khi hủy vé</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Khi Fan hủy vé (cancelBooking), cần khôi phục trạng thái Seat về AVAILABLE. Tuy nhiên nếu Seat không tìm thấy trong CSV thì xử lý thế nào để không crash chương trình?</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Trong phương thức cancelBooking(), sau khi mark Ticket là CANCELLED, làm thế nào để tìm và cập nhật Seat về AVAILABLE một cách an toàn khi SeatRepository.findById() trả về Optional&lt;Seat&gt;?</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>AI gợi ý dùng Optional.isPresent() để kiểm tra trước khi gọi .get(), nếu không tìm thấy ghế thì log cảnh báo nhưng vẫn tiếp tục hoàn tất việc hủy vé (Ticket vẫn CANCELLED).</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Critical Thinking: Gợi ý hợp lý. Tuy nhiên AI ban đầu viết seat = seatRepository.findById(id) và gán thẳng vào Seat mà không unwrap Optional, dẫn đến lỗi compile "incompatible types: Optional&lt;Seat&gt; cannot be converted to Seat".
+Contextualization: CsvRepository.findById() trả về Optional&lt;T&gt; theo thiết kế chuẩn của nhóm, em phải unwrap đúng cách.
+Creative Synthesis: Phát hiện lỗi compile ngay khi chạy javac, sửa lại bằng cách dùng seatOpt.isPresent() + seatOpt.get() đúng pattern Optional của Java 8.
+Decision: Áp dụng Optional pattern nhất quán cho tất cả các lời gọi findById() trong BookingController, vừa null-safe vừa đúng thiết kế repository.</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>BookingController.java phần cancelBooking() với Optional&lt;Seat&gt; seatOpt = seatRepository.findById() và Optional&lt;Ticket&gt; ticketOpt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1" s="20">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>View – Thiết kế Menu trong BookingView</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Cần thiết kế menu console cho BookingView tuân thủ quy tắc: View chỉ nhận input và hiển thị output, không chứa business logic.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Hãy thiết kế cấu trúc menu console cho BookingView với 2 chức năng: Đặt vé và Hủy vé. View phải hoàn toàn tách biệt khỏi logic xử lý và chỉ gọi xuống Controller.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>AI đề xuất cấu trúc vòng lặp while(true) với switch-case cho từng lựa chọn, mỗi case gọi một private method (handleBooking, handleCancellation) để tách riêng luồng nhập liệu.</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Critical Thinking: Thiết kế này đúng nhưng AI ban đầu đặt logic kiểm tra fanId.isEmpty() ngay trong handleBooking() của View — điều này vi phạm quy tắc số 6 của nhóm (View không được chứa business logic).
+Contextualization: Theo quy tắc nhóm, validation dữ liệu đầu vào thuộc về Controller hoặc Repository, View chỉ thu thập String và chuyển xuống.
+Creative Synthesis: Em loại bỏ hoàn toàn phần validation trong View, chỉ giữ lại scanner.nextLine() để đọc input và System.out.println() để hiển thị kết quả từ Controller.
+Decision: BookingView.handleBooking() chỉ gồm 3 lệnh đọc input (fanId, matchId, seatId) rồi gọi bookingController.bookSeat() và in kết quả — hoàn toàn không có if-else kiểm tra dữ liệu.</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>BookingView.java phần handleBooking() và handleCancellation() — chỉ có Scanner và System.out.println.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1" s="20">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>VERIFICATION</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>File I/O</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Xuất dữ liệu vé ra file PDF.</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Làm thế nào để xuất danh sách vé đã đặt ra file PDF trong Java một cách đơn giản mà không cần dùng thư viện ngoài?</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>AI gợi ý sử dụng class java.awt.print.PDFPrinterJob có sẵn trong Java JDK để trực tiếp tạo file PDF từ mã nguồn.</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Critical Thinking: HALLUCINATION DETECTED! Tìm trong tài liệu Oracle (JavaDoc) thì java.awt.print.PDFPrinterJob không tồn tại.
-Contextualization: AI bịa đặt ra một class không có thật để đáp ứng yêu cầu "không cần thư viện ngoài".
-Creative Synthesis: Nhận ra không thể tạo PDF dễ dàng bằng JDK chuẩn, em quyết định dùng thư viện iTextPDF.
-Decision: Bỏ qua gợi ý của AI, sử dụng thư viện ngoài iTextPDF.</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Kết quả tra cứu JavaDoc không có PDFPrinterJob, mã nguồn tích hợp iText.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1" s="19">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="80" customHeight="1" s="19">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-    </row>
-    <row r="9" ht="80" customHeight="1" s="19">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-    </row>
-    <row r="10" ht="80" customHeight="1" s="19">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>JUnit Test – Mock Repository bằng Anonymous Class</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Trong BookingTest, cần tạo môi trường test độc lập không ảnh hưởng đến data thật (seats.csv, tickets.csv thật). Cần cách tạo Repository giả trỏ vào file CSV tạm thời.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Làm thế nào để viết JUnit Test cho BookingController mà không cần dùng Mockito hay framework mock nào, chỉ dùng Java thuần, đảm bảo test không ghi đè lên file CSV thật của hệ thống?</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>AI gợi ý dùng Anonymous Class override phương thức getFilePath() trong @BeforeEach để trả về đường dẫn file CSV tạm thời (test_seats.csv...), và gọi File.delete() trước mỗi test để đảm bảo môi trường sạch.</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Critical Thinking: HALLUCINATION DETECTED! AI nói "dùng @AfterEach để xóa file sau test", nhưng nếu test fail giữa chừng thì @AfterEach vẫn chạy và xóa file — mất bằng chứng để debug. Tốt hơn nên xóa file ở @BeforeEach (trước khi test) thay vì @AfterEach (sau khi test).
+Contextualization: Pattern xóa file trong @BeforeEach đảm bảo mỗi test bắt đầu từ trạng thái sạch, đồng thời nếu test trước fail thì file vẫn còn để kiểm tra nguyên nhân.
+Creative Synthesis: Em đảo thứ tự: xóa file trong @BeforeEach (setup) thay vì @AfterEach (teardown). Anonymous Class pattern của AI rất hữu ích và không cần thêm dependency nào.
+Decision: Áp dụng @BeforeEach xóa file + Anonymous Class override getFilePath() — test hoàn toàn độc lập, chạy được bằng JUnit 5 với jar có sẵn trong lib/.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>BookingTest.java phần @BeforeEach setup() với 3 Anonymous Class SeatRepository, TicketRepository, TransactionRepository và 3 lệnh File.delete().</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1" s="20">
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
@@ -1146,7 +1252,7 @@
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
     </row>
-    <row r="11" ht="80" customHeight="1" s="19">
+    <row r="11" ht="80" customHeight="1" s="20">
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -1156,7 +1262,7 @@
       <c r="G11" s="7" t="n"/>
       <c r="H11" s="7" t="n"/>
     </row>
-    <row r="12" ht="80" customHeight="1" s="19">
+    <row r="12" ht="80" customHeight="1" s="20">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -1166,7 +1272,7 @@
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
     </row>
-    <row r="13" ht="80" customHeight="1" s="19">
+    <row r="13" ht="80" customHeight="1" s="20">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -1176,7 +1282,7 @@
       <c r="G13" s="7" t="n"/>
       <c r="H13" s="7" t="n"/>
     </row>
-    <row r="14" ht="80" customHeight="1" s="19">
+    <row r="14" ht="80" customHeight="1" s="20">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -1186,7 +1292,7 @@
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
     </row>
-    <row r="15" ht="80" customHeight="1" s="19">
+    <row r="15" ht="80" customHeight="1" s="20">
       <c r="A15" s="7" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -1196,7 +1302,7 @@
       <c r="G15" s="7" t="n"/>
       <c r="H15" s="7" t="n"/>
     </row>
-    <row r="16" ht="80" customHeight="1" s="19">
+    <row r="16" ht="80" customHeight="1" s="20">
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -1206,7 +1312,7 @@
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
     </row>
-    <row r="17" ht="80" customHeight="1" s="19">
+    <row r="17" ht="80" customHeight="1" s="20">
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -1216,7 +1322,7 @@
       <c r="G17" s="7" t="n"/>
       <c r="H17" s="7" t="n"/>
     </row>
-    <row r="18" ht="80" customHeight="1" s="19">
+    <row r="18" ht="80" customHeight="1" s="20">
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
@@ -1226,7 +1332,7 @@
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
     </row>
-    <row r="19" ht="80" customHeight="1" s="19">
+    <row r="19" ht="80" customHeight="1" s="20">
       <c r="A19" s="7" t="n"/>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -1236,7 +1342,7 @@
       <c r="G19" s="7" t="n"/>
       <c r="H19" s="7" t="n"/>
     </row>
-    <row r="20" ht="80" customHeight="1" s="19">
+    <row r="20" ht="80" customHeight="1" s="20">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
@@ -1246,7 +1352,7 @@
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
     </row>
-    <row r="21" ht="80" customHeight="1" s="19">
+    <row r="21" ht="80" customHeight="1" s="20">
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -1256,7 +1362,7 @@
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
     </row>
-    <row r="22" ht="80" customHeight="1" s="19">
+    <row r="22" ht="80" customHeight="1" s="20">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -1266,7 +1372,7 @@
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
     </row>
-    <row r="23" ht="80" customHeight="1" s="19">
+    <row r="23" ht="80" customHeight="1" s="20">
       <c r="A23" s="7" t="n"/>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="7" t="n"/>
@@ -1276,9 +1382,9 @@
       <c r="G23" s="7" t="n"/>
       <c r="H23" s="7" t="n"/>
     </row>
-    <row r="24" ht="80" customHeight="1" s="19"/>
-    <row r="25" ht="80" customHeight="1" s="19"/>
-    <row r="26" ht="80" customHeight="1" s="19"/>
+    <row r="24" ht="80" customHeight="1" s="20"/>
+    <row r="25" ht="80" customHeight="1" s="20"/>
+    <row r="26" ht="80" customHeight="1" s="20"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -1297,26 +1403,26 @@
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="19" min="1" max="1"/>
-    <col width="22" customWidth="1" style="19" min="2" max="2"/>
-    <col width="30" customWidth="1" style="19" min="3" max="6"/>
+    <col width="12" customWidth="1" style="20" min="1" max="1"/>
+    <col width="22" customWidth="1" style="20" min="2" max="2"/>
+    <col width="30" customWidth="1" style="20" min="3" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>MỖI PROJECT PHẢI PHÁT HIỆN ÍT NHẤT: Lab (≥1), Assignment (≥2), Project (≥3) cases hallucination</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1" s="19">
+    <row r="3" ht="40" customHeight="1" s="20">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Entry # (from Sheet 2)</t>
@@ -1348,47 +1454,71 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" s="19">
+    <row r="4" ht="60" customHeight="1" s="20">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>004</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Fabrication</t>
+          <t>API Misunderstanding</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Java có sẵn class java.awt.print.PDFPrinterJob để tạo file PDF mà không cần thư viện ngoài.</t>
+          <t>AI viết Seat seat = seatRepository.findById(id) và gán thẳng kết quả vào biến kiểu Seat, bỏ qua việc findById() trả về Optional&lt;Seat&gt;.</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Class PDFPrinterJob không hề tồn tại trong JDK tiêu chuẩn của Java.</t>
+          <t>findById() trong CsvRepository trả về Optional&lt;T&gt;, không thể gán trực tiếp vào Seat. Lỗi compile: "incompatible types: Optional&lt;Seat&gt; cannot be converted to Seat".</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Tra cứu trên Java SE Documentation và thử import class trong IDE (báo lỗi Cannot resolve symbol).</t>
+          <t>Phát hiện ngay khi chạy javac để compile BookingController.java — compiler báo lỗi incompatible types tại 3 vị trí gọi findById().</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Sử dụng thư viện ngoài được kiểm chứng là iTextPDF để xuất file PDF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="19">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-    </row>
-    <row r="6" ht="60" customHeight="1" s="19">
+          <t>Sửa lại toàn bộ 3 lời gọi findById() trong BookingController bằng Optional.isPresent() và .get() đúng chuẩn Optional Java 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1" s="20">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Wrong Lifecycle Advice</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>AI khuyến nghị dùng @AfterEach để xóa file CSV tạm thời sau mỗi JUnit test nhằm dọn dẹp môi trường.</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Xóa file trong @AfterEach sẽ xóa cả bằng chứng debug khi test fail. Đúng ra nên xóa trong @BeforeEach để đảm bảo môi trường sạch trước khi chạy, đồng thời giữ lại file của test trước (nếu fail) để phân tích.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Suy luận từ kinh nghiệm: nếu test fail, @AfterEach vẫn chạy và xóa file → mất log. Kiểm chứng bằng cách đọc lại JUnit 5 lifecycle documentation.</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Đổi thứ tự: xóa file CSV tạm thời trong @BeforeEach (trước khi test) thay vì @AfterEach. BookingTest hoạt động ổn định qua 5 lần chạy liên tiếp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" s="20">
       <c r="A6" s="7" t="n"/>
       <c r="B6" s="7" t="n"/>
       <c r="C6" s="7" t="n"/>
@@ -1396,7 +1526,7 @@
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
     </row>
-    <row r="7" ht="60" customHeight="1" s="19">
+    <row r="7" ht="60" customHeight="1" s="20">
       <c r="A7" s="7" t="n"/>
       <c r="B7" s="7" t="n"/>
       <c r="C7" s="7" t="n"/>
@@ -1404,7 +1534,7 @@
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
     </row>
-    <row r="8" ht="60" customHeight="1" s="19">
+    <row r="8" ht="60" customHeight="1" s="20">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="7" t="n"/>
@@ -1412,7 +1542,7 @@
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
     </row>
-    <row r="9" ht="60" customHeight="1" s="19">
+    <row r="9" ht="60" customHeight="1" s="20">
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="7" t="n"/>
@@ -1420,7 +1550,7 @@
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
     </row>
-    <row r="10" ht="60" customHeight="1" s="19">
+    <row r="10" ht="60" customHeight="1" s="20">
       <c r="A10" s="7" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="7" t="n"/>
@@ -1428,7 +1558,7 @@
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
     </row>
-    <row r="11" ht="60" customHeight="1" s="19">
+    <row r="11" ht="60" customHeight="1" s="20">
       <c r="A11" s="7" t="n"/>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
@@ -1436,7 +1566,7 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
     </row>
-    <row r="12" ht="60" customHeight="1" s="19">
+    <row r="12" ht="60" customHeight="1" s="20">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -1444,7 +1574,7 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
     </row>
-    <row r="13" ht="60" customHeight="1" s="19">
+    <row r="13" ht="60" customHeight="1" s="20">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="7" t="n"/>
@@ -1452,7 +1582,7 @@
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
     </row>
-    <row r="14" ht="60" customHeight="1" s="19">
+    <row r="14" ht="60" customHeight="1" s="20">
       <c r="A14" s="7" t="n"/>
       <c r="B14" s="7" t="n"/>
       <c r="C14" s="7" t="n"/>
@@ -1460,7 +1590,7 @@
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
     </row>
-    <row r="15" ht="60" customHeight="1" s="19">
+    <row r="15" ht="60" customHeight="1" s="20">
       <c r="A15" s="7" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="7" t="n"/>
@@ -1468,7 +1598,7 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
     </row>
-    <row r="16" ht="60" customHeight="1" s="19">
+    <row r="16" ht="60" customHeight="1" s="20">
       <c r="A16" s="7" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -1476,7 +1606,7 @@
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
     </row>
-    <row r="17" ht="60" customHeight="1" s="19">
+    <row r="17" ht="60" customHeight="1" s="20">
       <c r="A17" s="7" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="7" t="n"/>
@@ -1484,7 +1614,7 @@
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
     </row>
-    <row r="18" ht="60" customHeight="1" s="19">
+    <row r="18" ht="60" customHeight="1" s="20">
       <c r="A18" s="7" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="7" t="n"/>
@@ -1492,7 +1622,7 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
     </row>
-    <row r="19" ht="60" customHeight="1" s="19">
+    <row r="19" ht="60" customHeight="1" s="20">
       <c r="A19" s="7" t="n"/>
       <c r="B19" s="7" t="n"/>
       <c r="C19" s="7" t="n"/>
@@ -1500,7 +1630,7 @@
       <c r="E19" s="7" t="n"/>
       <c r="F19" s="7" t="n"/>
     </row>
-    <row r="20" ht="60" customHeight="1" s="19">
+    <row r="20" ht="60" customHeight="1" s="20">
       <c r="A20" s="7" t="n"/>
       <c r="B20" s="7" t="n"/>
       <c r="C20" s="7" t="n"/>
@@ -1508,7 +1638,7 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
     </row>
-    <row r="21" ht="60" customHeight="1" s="19">
+    <row r="21" ht="60" customHeight="1" s="20">
       <c r="A21" s="7" t="n"/>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="7" t="n"/>
@@ -1516,7 +1646,7 @@
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
     </row>
-    <row r="22" ht="60" customHeight="1" s="19">
+    <row r="22" ht="60" customHeight="1" s="20">
       <c r="A22" s="7" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="7" t="n"/>
@@ -1524,16 +1654,16 @@
       <c r="E22" s="7" t="n"/>
       <c r="F22" s="7" t="n"/>
     </row>
-    <row r="23" ht="60" customHeight="1" s="19"/>
-    <row r="24" ht="60" customHeight="1" s="19"/>
-    <row r="28">
+    <row r="23" ht="60" customHeight="1" s="20"/>
+    <row r="24" ht="60" customHeight="1" s="20"/>
+    <row r="28" ht="19" customHeight="1" s="20">
       <c r="A28" s="1" t="inlineStr">
         <is>
           <t>HALLUCINATION TYPES REFERENCE:</t>
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="16" customHeight="1" s="20">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Type</t>
@@ -1550,7 +1680,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="19" customHeight="1" s="19">
+    <row r="30" ht="19" customHeight="1" s="20">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>Fabrication</t>
@@ -1567,7 +1697,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1" s="19">
+    <row r="31" ht="16" customHeight="1" s="20">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Oversimplification</t>
@@ -1584,7 +1714,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="32" customHeight="1" s="19">
+    <row r="32" ht="32" customHeight="1" s="20">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t>Logic Error</t>
@@ -1601,7 +1731,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1" s="19">
+    <row r="33" ht="32" customHeight="1" s="20">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Outdated Info</t>
@@ -1618,7 +1748,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1" s="19">
+    <row r="34" ht="32" customHeight="1" s="20">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Context Misunderstanding</t>
@@ -1635,8 +1765,8 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1" s="19"/>
-    <row r="36" ht="48" customHeight="1" s="19"/>
+    <row r="35" ht="32" customHeight="1" s="20"/>
+    <row r="36" ht="48" customHeight="1" s="20"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
@@ -1655,34 +1785,34 @@
   <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" style="19" min="1" max="1"/>
-    <col width="60" customWidth="1" style="19" min="2" max="2"/>
-    <col width="10" customWidth="1" style="19" min="3" max="3"/>
-    <col width="30" customWidth="1" style="19" min="4" max="4"/>
+    <col width="8" customWidth="1" style="20" min="1" max="1"/>
+    <col width="60" customWidth="1" style="20" min="2" max="2"/>
+    <col width="10" customWidth="1" style="20" min="3" max="3"/>
+    <col width="30" customWidth="1" style="20" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>SELF-ASSESSMENT CHECKLIST (Trước khi nộp)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>Kiểm tra kỹ trước khi nộp. MỖI ENTRY phải pass ≥4/5 tiêu chí dưới đây.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="19" customHeight="1" s="19">
+    <row r="4" ht="19" customHeight="1" s="20">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>A. KIỂM TRA CHẤT LƯỢNG MỖI ENTRY (Pass ≥4/5)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="19">
+    <row r="5" ht="16" customHeight="1" s="20">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>#</t>
@@ -1794,14 +1924,14 @@
       </c>
       <c r="D10" s="13" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1" s="19">
+    <row r="12" ht="19" customHeight="1" s="20">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>B. KIỂM TRA TỔNG THỂ LOG</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1" s="19">
+    <row r="13" ht="16" customHeight="1" s="20">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t>#</t>
@@ -1913,7 +2043,7 @@
       </c>
       <c r="D18" s="13" t="n"/>
     </row>
-    <row r="20" ht="16" customHeight="1" s="19">
+    <row r="20" ht="16" customHeight="1" s="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
           <t>⚠️ LƯU Ý QUAN TRỌNG:</t>
@@ -1934,7 +2064,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="19" customHeight="1" s="19">
+    <row r="25" ht="19" customHeight="1" s="20">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>C. CHUẨN BỊ CHO ORAL VIVAS (Q&amp;A)</t>
@@ -1948,7 +2078,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1" s="19">
+    <row r="27" ht="48" customHeight="1" s="20">
       <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Entry #</t>
@@ -1970,7 +2100,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1" s="19">
+    <row r="28" ht="16" customHeight="1" s="20">
       <c r="A28" s="9" t="inlineStr">
         <is>
           <t>001</t>
@@ -1980,7 +2110,7 @@
       <c r="C28" s="7" t="n"/>
       <c r="D28" s="7" t="n"/>
     </row>
-    <row r="29" ht="16" customHeight="1" s="19">
+    <row r="29" ht="16" customHeight="1" s="20">
       <c r="A29" s="9" t="inlineStr">
         <is>
           <t>002</t>
@@ -1990,7 +2120,7 @@
       <c r="C29" s="7" t="n"/>
       <c r="D29" s="7" t="n"/>
     </row>
-    <row r="30" ht="16" customHeight="1" s="19">
+    <row r="30" ht="16" customHeight="1" s="20">
       <c r="A30" s="9" t="inlineStr">
         <is>
           <t>003</t>
